--- a/2026 PAD statements submission tracker.xlsx
+++ b/2026 PAD statements submission tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cigpsa-my.sharepoint.com/personal/kate_zhang_cigp_com/Documents/Desktop/PAD Automation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7636" documentId="6_{8AE067CB-1B34-4B4E-8DCC-FD96BA211385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74432934-361E-4C29-A921-41B877946654}"/>
+  <xr:revisionPtr revIDLastSave="7664" documentId="6_{8AE067CB-1B34-4B4E-8DCC-FD96BA211385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5B7075D-F466-4F19-B208-E0345CECDE10}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" activeTab="1" xr2:uid="{D6B58562-8BF8-4E58-90CD-D9AC34519CBC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" activeTab="1" xr2:uid="{D6B58562-8BF8-4E58-90CD-D9AC34519CBC}"/>
   </bookViews>
   <sheets>
     <sheet name="Statement Records" sheetId="1" r:id="rId1"/>
@@ -118,7 +118,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2415" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2424" uniqueCount="547">
   <si>
     <t>Staff Names as per CIGP</t>
   </si>
@@ -1765,6 +1765,9 @@
   </si>
   <si>
     <t>611539677888</t>
+  </si>
+  <si>
+    <t>Kobe Yip</t>
   </si>
 </sst>
 </file>
@@ -2184,7 +2187,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2410,29 +2413,8 @@
     <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="17" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2461,6 +2443,15 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2478,6 +2469,36 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="17" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -18840,6 +18861,644 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9AF1C936-48D0-4E9A-940D-17EC0AB10BEB}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
+  <location ref="A50:B63" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="8">
+    <pivotField multipleItemSelectionAllowed="1" showAll="0">
+      <items count="29">
+        <item sd="0" x="12"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="0"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" dataField="1" numFmtId="166" showAll="0">
+      <items count="116">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="369">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item sd="0" x="14"/>
+        <item sd="0" x="15"/>
+        <item sd="0" x="16"/>
+        <item sd="0" x="17"/>
+        <item sd="0" x="18"/>
+        <item sd="0" x="19"/>
+        <item sd="0" x="20"/>
+        <item sd="0" x="21"/>
+        <item sd="0" x="22"/>
+        <item sd="0" x="23"/>
+        <item sd="0" x="24"/>
+        <item sd="0" x="25"/>
+        <item sd="0" x="26"/>
+        <item sd="0" x="27"/>
+        <item sd="0" x="28"/>
+        <item sd="0" x="29"/>
+        <item sd="0" x="30"/>
+        <item sd="0" x="31"/>
+        <item sd="0" x="32"/>
+        <item sd="0" x="33"/>
+        <item sd="0" x="34"/>
+        <item sd="0" x="35"/>
+        <item sd="0" x="36"/>
+        <item sd="0" x="37"/>
+        <item sd="0" x="38"/>
+        <item sd="0" x="39"/>
+        <item sd="0" x="40"/>
+        <item sd="0" x="41"/>
+        <item sd="0" x="42"/>
+        <item sd="0" x="43"/>
+        <item sd="0" x="44"/>
+        <item sd="0" x="45"/>
+        <item sd="0" x="46"/>
+        <item sd="0" x="47"/>
+        <item sd="0" x="48"/>
+        <item sd="0" x="49"/>
+        <item sd="0" x="50"/>
+        <item sd="0" x="51"/>
+        <item sd="0" x="52"/>
+        <item sd="0" x="53"/>
+        <item sd="0" x="54"/>
+        <item sd="0" x="55"/>
+        <item sd="0" x="56"/>
+        <item sd="0" x="57"/>
+        <item sd="0" x="58"/>
+        <item sd="0" x="59"/>
+        <item sd="0" x="60"/>
+        <item sd="0" x="61"/>
+        <item sd="0" x="62"/>
+        <item sd="0" x="63"/>
+        <item sd="0" x="64"/>
+        <item sd="0" x="65"/>
+        <item sd="0" x="66"/>
+        <item sd="0" x="67"/>
+        <item sd="0" x="68"/>
+        <item sd="0" x="69"/>
+        <item sd="0" x="70"/>
+        <item sd="0" x="71"/>
+        <item sd="0" x="72"/>
+        <item sd="0" x="73"/>
+        <item sd="0" x="74"/>
+        <item sd="0" x="75"/>
+        <item sd="0" x="76"/>
+        <item sd="0" x="77"/>
+        <item sd="0" x="78"/>
+        <item sd="0" x="79"/>
+        <item sd="0" x="80"/>
+        <item sd="0" x="81"/>
+        <item sd="0" x="82"/>
+        <item sd="0" x="83"/>
+        <item sd="0" x="84"/>
+        <item sd="0" x="85"/>
+        <item sd="0" x="86"/>
+        <item sd="0" x="87"/>
+        <item sd="0" x="88"/>
+        <item sd="0" x="89"/>
+        <item sd="0" x="90"/>
+        <item sd="0" x="91"/>
+        <item sd="0" x="92"/>
+        <item sd="0" x="93"/>
+        <item sd="0" x="94"/>
+        <item sd="0" x="95"/>
+        <item sd="0" x="96"/>
+        <item sd="0" x="97"/>
+        <item sd="0" x="98"/>
+        <item sd="0" x="99"/>
+        <item sd="0" x="100"/>
+        <item sd="0" x="101"/>
+        <item sd="0" x="102"/>
+        <item sd="0" x="103"/>
+        <item sd="0" x="104"/>
+        <item sd="0" x="105"/>
+        <item sd="0" x="106"/>
+        <item sd="0" x="107"/>
+        <item sd="0" x="108"/>
+        <item sd="0" x="109"/>
+        <item sd="0" x="110"/>
+        <item sd="0" x="111"/>
+        <item sd="0" x="112"/>
+        <item sd="0" x="113"/>
+        <item sd="0" x="114"/>
+        <item sd="0" x="115"/>
+        <item sd="0" x="116"/>
+        <item sd="0" x="117"/>
+        <item sd="0" x="118"/>
+        <item sd="0" x="119"/>
+        <item sd="0" x="120"/>
+        <item sd="0" x="121"/>
+        <item sd="0" x="122"/>
+        <item sd="0" x="123"/>
+        <item sd="0" x="124"/>
+        <item sd="0" x="125"/>
+        <item sd="0" x="126"/>
+        <item sd="0" x="127"/>
+        <item sd="0" x="128"/>
+        <item sd="0" x="129"/>
+        <item sd="0" x="130"/>
+        <item sd="0" x="131"/>
+        <item sd="0" x="132"/>
+        <item sd="0" x="133"/>
+        <item sd="0" x="134"/>
+        <item sd="0" x="135"/>
+        <item sd="0" x="136"/>
+        <item sd="0" x="137"/>
+        <item sd="0" x="138"/>
+        <item sd="0" x="139"/>
+        <item sd="0" x="140"/>
+        <item sd="0" x="141"/>
+        <item sd="0" x="142"/>
+        <item sd="0" x="143"/>
+        <item sd="0" x="144"/>
+        <item sd="0" x="145"/>
+        <item sd="0" x="146"/>
+        <item sd="0" x="147"/>
+        <item sd="0" x="148"/>
+        <item sd="0" x="149"/>
+        <item sd="0" x="150"/>
+        <item sd="0" x="151"/>
+        <item sd="0" x="152"/>
+        <item sd="0" x="153"/>
+        <item sd="0" x="154"/>
+        <item sd="0" x="155"/>
+        <item sd="0" x="156"/>
+        <item sd="0" x="157"/>
+        <item sd="0" x="158"/>
+        <item sd="0" x="159"/>
+        <item sd="0" x="160"/>
+        <item sd="0" x="161"/>
+        <item sd="0" x="162"/>
+        <item sd="0" x="163"/>
+        <item sd="0" x="164"/>
+        <item sd="0" x="165"/>
+        <item sd="0" x="166"/>
+        <item sd="0" x="167"/>
+        <item sd="0" x="168"/>
+        <item sd="0" x="169"/>
+        <item sd="0" x="170"/>
+        <item sd="0" x="171"/>
+        <item sd="0" x="172"/>
+        <item sd="0" x="173"/>
+        <item sd="0" x="174"/>
+        <item sd="0" x="175"/>
+        <item sd="0" x="176"/>
+        <item sd="0" x="177"/>
+        <item sd="0" x="178"/>
+        <item sd="0" x="179"/>
+        <item sd="0" x="180"/>
+        <item sd="0" x="181"/>
+        <item sd="0" x="182"/>
+        <item sd="0" x="183"/>
+        <item sd="0" x="184"/>
+        <item sd="0" x="185"/>
+        <item sd="0" x="186"/>
+        <item sd="0" x="187"/>
+        <item sd="0" x="188"/>
+        <item sd="0" x="189"/>
+        <item sd="0" x="190"/>
+        <item sd="0" x="191"/>
+        <item sd="0" x="192"/>
+        <item sd="0" x="193"/>
+        <item sd="0" x="194"/>
+        <item sd="0" x="195"/>
+        <item sd="0" x="196"/>
+        <item sd="0" x="197"/>
+        <item sd="0" x="198"/>
+        <item sd="0" x="199"/>
+        <item sd="0" x="200"/>
+        <item sd="0" x="201"/>
+        <item sd="0" x="202"/>
+        <item sd="0" x="203"/>
+        <item sd="0" x="204"/>
+        <item sd="0" x="205"/>
+        <item sd="0" x="206"/>
+        <item sd="0" x="207"/>
+        <item sd="0" x="208"/>
+        <item sd="0" x="209"/>
+        <item sd="0" x="210"/>
+        <item sd="0" x="211"/>
+        <item sd="0" x="212"/>
+        <item sd="0" x="213"/>
+        <item sd="0" x="214"/>
+        <item sd="0" x="215"/>
+        <item sd="0" x="216"/>
+        <item sd="0" x="217"/>
+        <item sd="0" x="218"/>
+        <item sd="0" x="219"/>
+        <item sd="0" x="220"/>
+        <item sd="0" x="221"/>
+        <item sd="0" x="222"/>
+        <item sd="0" x="223"/>
+        <item sd="0" x="224"/>
+        <item sd="0" x="225"/>
+        <item sd="0" x="226"/>
+        <item sd="0" x="227"/>
+        <item sd="0" x="228"/>
+        <item sd="0" x="229"/>
+        <item sd="0" x="230"/>
+        <item sd="0" x="231"/>
+        <item sd="0" x="232"/>
+        <item sd="0" x="233"/>
+        <item sd="0" x="234"/>
+        <item sd="0" x="235"/>
+        <item sd="0" x="236"/>
+        <item sd="0" x="237"/>
+        <item sd="0" x="238"/>
+        <item sd="0" x="239"/>
+        <item sd="0" x="240"/>
+        <item sd="0" x="241"/>
+        <item sd="0" x="242"/>
+        <item sd="0" x="243"/>
+        <item sd="0" x="244"/>
+        <item sd="0" x="245"/>
+        <item sd="0" x="246"/>
+        <item sd="0" x="247"/>
+        <item sd="0" x="248"/>
+        <item sd="0" x="249"/>
+        <item sd="0" x="250"/>
+        <item sd="0" x="251"/>
+        <item sd="0" x="252"/>
+        <item sd="0" x="253"/>
+        <item sd="0" x="254"/>
+        <item sd="0" x="255"/>
+        <item sd="0" x="256"/>
+        <item sd="0" x="257"/>
+        <item sd="0" x="258"/>
+        <item sd="0" x="259"/>
+        <item sd="0" x="260"/>
+        <item sd="0" x="261"/>
+        <item sd="0" x="262"/>
+        <item sd="0" x="263"/>
+        <item sd="0" x="264"/>
+        <item sd="0" x="265"/>
+        <item sd="0" x="266"/>
+        <item sd="0" x="267"/>
+        <item sd="0" x="268"/>
+        <item sd="0" x="269"/>
+        <item sd="0" x="270"/>
+        <item sd="0" x="271"/>
+        <item sd="0" x="272"/>
+        <item sd="0" x="273"/>
+        <item sd="0" x="274"/>
+        <item sd="0" x="275"/>
+        <item sd="0" x="276"/>
+        <item sd="0" x="277"/>
+        <item sd="0" x="278"/>
+        <item sd="0" x="279"/>
+        <item sd="0" x="280"/>
+        <item sd="0" x="281"/>
+        <item sd="0" x="282"/>
+        <item sd="0" x="283"/>
+        <item sd="0" x="284"/>
+        <item sd="0" x="285"/>
+        <item sd="0" x="286"/>
+        <item sd="0" x="287"/>
+        <item sd="0" x="288"/>
+        <item sd="0" x="289"/>
+        <item sd="0" x="290"/>
+        <item sd="0" x="291"/>
+        <item sd="0" x="292"/>
+        <item sd="0" x="293"/>
+        <item sd="0" x="294"/>
+        <item sd="0" x="295"/>
+        <item sd="0" x="296"/>
+        <item sd="0" x="297"/>
+        <item sd="0" x="298"/>
+        <item sd="0" x="299"/>
+        <item sd="0" x="300"/>
+        <item sd="0" x="301"/>
+        <item sd="0" x="302"/>
+        <item sd="0" x="303"/>
+        <item sd="0" x="304"/>
+        <item sd="0" x="305"/>
+        <item sd="0" x="306"/>
+        <item sd="0" x="307"/>
+        <item sd="0" x="308"/>
+        <item sd="0" x="309"/>
+        <item sd="0" x="310"/>
+        <item sd="0" x="311"/>
+        <item sd="0" x="312"/>
+        <item sd="0" x="313"/>
+        <item sd="0" x="314"/>
+        <item sd="0" x="315"/>
+        <item sd="0" x="316"/>
+        <item sd="0" x="317"/>
+        <item sd="0" x="318"/>
+        <item sd="0" x="319"/>
+        <item sd="0" x="320"/>
+        <item sd="0" x="321"/>
+        <item sd="0" x="322"/>
+        <item sd="0" x="323"/>
+        <item sd="0" x="324"/>
+        <item sd="0" x="325"/>
+        <item sd="0" x="326"/>
+        <item sd="0" x="327"/>
+        <item sd="0" x="328"/>
+        <item sd="0" x="329"/>
+        <item sd="0" x="330"/>
+        <item sd="0" x="331"/>
+        <item sd="0" x="332"/>
+        <item sd="0" x="333"/>
+        <item sd="0" x="334"/>
+        <item sd="0" x="335"/>
+        <item sd="0" x="336"/>
+        <item sd="0" x="337"/>
+        <item sd="0" x="338"/>
+        <item sd="0" x="339"/>
+        <item sd="0" x="340"/>
+        <item sd="0" x="341"/>
+        <item sd="0" x="342"/>
+        <item sd="0" x="343"/>
+        <item sd="0" x="344"/>
+        <item sd="0" x="345"/>
+        <item sd="0" x="346"/>
+        <item sd="0" x="347"/>
+        <item sd="0" x="348"/>
+        <item sd="0" x="349"/>
+        <item sd="0" x="350"/>
+        <item sd="0" x="351"/>
+        <item sd="0" x="352"/>
+        <item sd="0" x="353"/>
+        <item sd="0" x="354"/>
+        <item sd="0" x="355"/>
+        <item sd="0" x="356"/>
+        <item sd="0" x="357"/>
+        <item sd="0" x="358"/>
+        <item sd="0" x="359"/>
+        <item sd="0" x="360"/>
+        <item sd="0" x="361"/>
+        <item sd="0" x="362"/>
+        <item sd="0" x="363"/>
+        <item sd="0" x="364"/>
+        <item sd="0" x="365"/>
+        <item sd="0" x="366"/>
+        <item sd="0" x="367"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="15">
+        <item sd="0" x="0"/>
+        <item sd="0" x="1"/>
+        <item sd="0" x="2"/>
+        <item sd="0" x="3"/>
+        <item sd="0" x="4"/>
+        <item sd="0" x="5"/>
+        <item sd="0" x="6"/>
+        <item sd="0" x="7"/>
+        <item sd="0" x="8"/>
+        <item sd="0" x="9"/>
+        <item sd="0" x="10"/>
+        <item sd="0" x="11"/>
+        <item sd="0" x="12"/>
+        <item sd="0" x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="3">
+    <field x="7"/>
+    <field x="6"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="13">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Request Date" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="5" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="10" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AC03B5AF-37D7-48CA-B785-1A722AE061CF}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="A3:B32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
@@ -19517,644 +20176,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9AF1C936-48D0-4E9A-940D-17EC0AB10BEB}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
-  <location ref="A50:B63" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="8">
-    <pivotField multipleItemSelectionAllowed="1" showAll="0">
-      <items count="29">
-        <item sd="0" x="12"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="27"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="16"/>
-        <item sd="0" x="17"/>
-        <item sd="0" x="0"/>
-        <item sd="0" x="20"/>
-        <item sd="0" x="15"/>
-        <item sd="0" x="19"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="22"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="24"/>
-        <item sd="0" x="26"/>
-        <item sd="0" x="23"/>
-        <item sd="0" x="21"/>
-        <item sd="0" x="18"/>
-        <item sd="0" x="25"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="14"/>
-        <item sd="0" x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" dataField="1" numFmtId="166" showAll="0">
-      <items count="116">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="369">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="13"/>
-        <item sd="0" x="14"/>
-        <item sd="0" x="15"/>
-        <item sd="0" x="16"/>
-        <item sd="0" x="17"/>
-        <item sd="0" x="18"/>
-        <item sd="0" x="19"/>
-        <item sd="0" x="20"/>
-        <item sd="0" x="21"/>
-        <item sd="0" x="22"/>
-        <item sd="0" x="23"/>
-        <item sd="0" x="24"/>
-        <item sd="0" x="25"/>
-        <item sd="0" x="26"/>
-        <item sd="0" x="27"/>
-        <item sd="0" x="28"/>
-        <item sd="0" x="29"/>
-        <item sd="0" x="30"/>
-        <item sd="0" x="31"/>
-        <item sd="0" x="32"/>
-        <item sd="0" x="33"/>
-        <item sd="0" x="34"/>
-        <item sd="0" x="35"/>
-        <item sd="0" x="36"/>
-        <item sd="0" x="37"/>
-        <item sd="0" x="38"/>
-        <item sd="0" x="39"/>
-        <item sd="0" x="40"/>
-        <item sd="0" x="41"/>
-        <item sd="0" x="42"/>
-        <item sd="0" x="43"/>
-        <item sd="0" x="44"/>
-        <item sd="0" x="45"/>
-        <item sd="0" x="46"/>
-        <item sd="0" x="47"/>
-        <item sd="0" x="48"/>
-        <item sd="0" x="49"/>
-        <item sd="0" x="50"/>
-        <item sd="0" x="51"/>
-        <item sd="0" x="52"/>
-        <item sd="0" x="53"/>
-        <item sd="0" x="54"/>
-        <item sd="0" x="55"/>
-        <item sd="0" x="56"/>
-        <item sd="0" x="57"/>
-        <item sd="0" x="58"/>
-        <item sd="0" x="59"/>
-        <item sd="0" x="60"/>
-        <item sd="0" x="61"/>
-        <item sd="0" x="62"/>
-        <item sd="0" x="63"/>
-        <item sd="0" x="64"/>
-        <item sd="0" x="65"/>
-        <item sd="0" x="66"/>
-        <item sd="0" x="67"/>
-        <item sd="0" x="68"/>
-        <item sd="0" x="69"/>
-        <item sd="0" x="70"/>
-        <item sd="0" x="71"/>
-        <item sd="0" x="72"/>
-        <item sd="0" x="73"/>
-        <item sd="0" x="74"/>
-        <item sd="0" x="75"/>
-        <item sd="0" x="76"/>
-        <item sd="0" x="77"/>
-        <item sd="0" x="78"/>
-        <item sd="0" x="79"/>
-        <item sd="0" x="80"/>
-        <item sd="0" x="81"/>
-        <item sd="0" x="82"/>
-        <item sd="0" x="83"/>
-        <item sd="0" x="84"/>
-        <item sd="0" x="85"/>
-        <item sd="0" x="86"/>
-        <item sd="0" x="87"/>
-        <item sd="0" x="88"/>
-        <item sd="0" x="89"/>
-        <item sd="0" x="90"/>
-        <item sd="0" x="91"/>
-        <item sd="0" x="92"/>
-        <item sd="0" x="93"/>
-        <item sd="0" x="94"/>
-        <item sd="0" x="95"/>
-        <item sd="0" x="96"/>
-        <item sd="0" x="97"/>
-        <item sd="0" x="98"/>
-        <item sd="0" x="99"/>
-        <item sd="0" x="100"/>
-        <item sd="0" x="101"/>
-        <item sd="0" x="102"/>
-        <item sd="0" x="103"/>
-        <item sd="0" x="104"/>
-        <item sd="0" x="105"/>
-        <item sd="0" x="106"/>
-        <item sd="0" x="107"/>
-        <item sd="0" x="108"/>
-        <item sd="0" x="109"/>
-        <item sd="0" x="110"/>
-        <item sd="0" x="111"/>
-        <item sd="0" x="112"/>
-        <item sd="0" x="113"/>
-        <item sd="0" x="114"/>
-        <item sd="0" x="115"/>
-        <item sd="0" x="116"/>
-        <item sd="0" x="117"/>
-        <item sd="0" x="118"/>
-        <item sd="0" x="119"/>
-        <item sd="0" x="120"/>
-        <item sd="0" x="121"/>
-        <item sd="0" x="122"/>
-        <item sd="0" x="123"/>
-        <item sd="0" x="124"/>
-        <item sd="0" x="125"/>
-        <item sd="0" x="126"/>
-        <item sd="0" x="127"/>
-        <item sd="0" x="128"/>
-        <item sd="0" x="129"/>
-        <item sd="0" x="130"/>
-        <item sd="0" x="131"/>
-        <item sd="0" x="132"/>
-        <item sd="0" x="133"/>
-        <item sd="0" x="134"/>
-        <item sd="0" x="135"/>
-        <item sd="0" x="136"/>
-        <item sd="0" x="137"/>
-        <item sd="0" x="138"/>
-        <item sd="0" x="139"/>
-        <item sd="0" x="140"/>
-        <item sd="0" x="141"/>
-        <item sd="0" x="142"/>
-        <item sd="0" x="143"/>
-        <item sd="0" x="144"/>
-        <item sd="0" x="145"/>
-        <item sd="0" x="146"/>
-        <item sd="0" x="147"/>
-        <item sd="0" x="148"/>
-        <item sd="0" x="149"/>
-        <item sd="0" x="150"/>
-        <item sd="0" x="151"/>
-        <item sd="0" x="152"/>
-        <item sd="0" x="153"/>
-        <item sd="0" x="154"/>
-        <item sd="0" x="155"/>
-        <item sd="0" x="156"/>
-        <item sd="0" x="157"/>
-        <item sd="0" x="158"/>
-        <item sd="0" x="159"/>
-        <item sd="0" x="160"/>
-        <item sd="0" x="161"/>
-        <item sd="0" x="162"/>
-        <item sd="0" x="163"/>
-        <item sd="0" x="164"/>
-        <item sd="0" x="165"/>
-        <item sd="0" x="166"/>
-        <item sd="0" x="167"/>
-        <item sd="0" x="168"/>
-        <item sd="0" x="169"/>
-        <item sd="0" x="170"/>
-        <item sd="0" x="171"/>
-        <item sd="0" x="172"/>
-        <item sd="0" x="173"/>
-        <item sd="0" x="174"/>
-        <item sd="0" x="175"/>
-        <item sd="0" x="176"/>
-        <item sd="0" x="177"/>
-        <item sd="0" x="178"/>
-        <item sd="0" x="179"/>
-        <item sd="0" x="180"/>
-        <item sd="0" x="181"/>
-        <item sd="0" x="182"/>
-        <item sd="0" x="183"/>
-        <item sd="0" x="184"/>
-        <item sd="0" x="185"/>
-        <item sd="0" x="186"/>
-        <item sd="0" x="187"/>
-        <item sd="0" x="188"/>
-        <item sd="0" x="189"/>
-        <item sd="0" x="190"/>
-        <item sd="0" x="191"/>
-        <item sd="0" x="192"/>
-        <item sd="0" x="193"/>
-        <item sd="0" x="194"/>
-        <item sd="0" x="195"/>
-        <item sd="0" x="196"/>
-        <item sd="0" x="197"/>
-        <item sd="0" x="198"/>
-        <item sd="0" x="199"/>
-        <item sd="0" x="200"/>
-        <item sd="0" x="201"/>
-        <item sd="0" x="202"/>
-        <item sd="0" x="203"/>
-        <item sd="0" x="204"/>
-        <item sd="0" x="205"/>
-        <item sd="0" x="206"/>
-        <item sd="0" x="207"/>
-        <item sd="0" x="208"/>
-        <item sd="0" x="209"/>
-        <item sd="0" x="210"/>
-        <item sd="0" x="211"/>
-        <item sd="0" x="212"/>
-        <item sd="0" x="213"/>
-        <item sd="0" x="214"/>
-        <item sd="0" x="215"/>
-        <item sd="0" x="216"/>
-        <item sd="0" x="217"/>
-        <item sd="0" x="218"/>
-        <item sd="0" x="219"/>
-        <item sd="0" x="220"/>
-        <item sd="0" x="221"/>
-        <item sd="0" x="222"/>
-        <item sd="0" x="223"/>
-        <item sd="0" x="224"/>
-        <item sd="0" x="225"/>
-        <item sd="0" x="226"/>
-        <item sd="0" x="227"/>
-        <item sd="0" x="228"/>
-        <item sd="0" x="229"/>
-        <item sd="0" x="230"/>
-        <item sd="0" x="231"/>
-        <item sd="0" x="232"/>
-        <item sd="0" x="233"/>
-        <item sd="0" x="234"/>
-        <item sd="0" x="235"/>
-        <item sd="0" x="236"/>
-        <item sd="0" x="237"/>
-        <item sd="0" x="238"/>
-        <item sd="0" x="239"/>
-        <item sd="0" x="240"/>
-        <item sd="0" x="241"/>
-        <item sd="0" x="242"/>
-        <item sd="0" x="243"/>
-        <item sd="0" x="244"/>
-        <item sd="0" x="245"/>
-        <item sd="0" x="246"/>
-        <item sd="0" x="247"/>
-        <item sd="0" x="248"/>
-        <item sd="0" x="249"/>
-        <item sd="0" x="250"/>
-        <item sd="0" x="251"/>
-        <item sd="0" x="252"/>
-        <item sd="0" x="253"/>
-        <item sd="0" x="254"/>
-        <item sd="0" x="255"/>
-        <item sd="0" x="256"/>
-        <item sd="0" x="257"/>
-        <item sd="0" x="258"/>
-        <item sd="0" x="259"/>
-        <item sd="0" x="260"/>
-        <item sd="0" x="261"/>
-        <item sd="0" x="262"/>
-        <item sd="0" x="263"/>
-        <item sd="0" x="264"/>
-        <item sd="0" x="265"/>
-        <item sd="0" x="266"/>
-        <item sd="0" x="267"/>
-        <item sd="0" x="268"/>
-        <item sd="0" x="269"/>
-        <item sd="0" x="270"/>
-        <item sd="0" x="271"/>
-        <item sd="0" x="272"/>
-        <item sd="0" x="273"/>
-        <item sd="0" x="274"/>
-        <item sd="0" x="275"/>
-        <item sd="0" x="276"/>
-        <item sd="0" x="277"/>
-        <item sd="0" x="278"/>
-        <item sd="0" x="279"/>
-        <item sd="0" x="280"/>
-        <item sd="0" x="281"/>
-        <item sd="0" x="282"/>
-        <item sd="0" x="283"/>
-        <item sd="0" x="284"/>
-        <item sd="0" x="285"/>
-        <item sd="0" x="286"/>
-        <item sd="0" x="287"/>
-        <item sd="0" x="288"/>
-        <item sd="0" x="289"/>
-        <item sd="0" x="290"/>
-        <item sd="0" x="291"/>
-        <item sd="0" x="292"/>
-        <item sd="0" x="293"/>
-        <item sd="0" x="294"/>
-        <item sd="0" x="295"/>
-        <item sd="0" x="296"/>
-        <item sd="0" x="297"/>
-        <item sd="0" x="298"/>
-        <item sd="0" x="299"/>
-        <item sd="0" x="300"/>
-        <item sd="0" x="301"/>
-        <item sd="0" x="302"/>
-        <item sd="0" x="303"/>
-        <item sd="0" x="304"/>
-        <item sd="0" x="305"/>
-        <item sd="0" x="306"/>
-        <item sd="0" x="307"/>
-        <item sd="0" x="308"/>
-        <item sd="0" x="309"/>
-        <item sd="0" x="310"/>
-        <item sd="0" x="311"/>
-        <item sd="0" x="312"/>
-        <item sd="0" x="313"/>
-        <item sd="0" x="314"/>
-        <item sd="0" x="315"/>
-        <item sd="0" x="316"/>
-        <item sd="0" x="317"/>
-        <item sd="0" x="318"/>
-        <item sd="0" x="319"/>
-        <item sd="0" x="320"/>
-        <item sd="0" x="321"/>
-        <item sd="0" x="322"/>
-        <item sd="0" x="323"/>
-        <item sd="0" x="324"/>
-        <item sd="0" x="325"/>
-        <item sd="0" x="326"/>
-        <item sd="0" x="327"/>
-        <item sd="0" x="328"/>
-        <item sd="0" x="329"/>
-        <item sd="0" x="330"/>
-        <item sd="0" x="331"/>
-        <item sd="0" x="332"/>
-        <item sd="0" x="333"/>
-        <item sd="0" x="334"/>
-        <item sd="0" x="335"/>
-        <item sd="0" x="336"/>
-        <item sd="0" x="337"/>
-        <item sd="0" x="338"/>
-        <item sd="0" x="339"/>
-        <item sd="0" x="340"/>
-        <item sd="0" x="341"/>
-        <item sd="0" x="342"/>
-        <item sd="0" x="343"/>
-        <item sd="0" x="344"/>
-        <item sd="0" x="345"/>
-        <item sd="0" x="346"/>
-        <item sd="0" x="347"/>
-        <item sd="0" x="348"/>
-        <item sd="0" x="349"/>
-        <item sd="0" x="350"/>
-        <item sd="0" x="351"/>
-        <item sd="0" x="352"/>
-        <item sd="0" x="353"/>
-        <item sd="0" x="354"/>
-        <item sd="0" x="355"/>
-        <item sd="0" x="356"/>
-        <item sd="0" x="357"/>
-        <item sd="0" x="358"/>
-        <item sd="0" x="359"/>
-        <item sd="0" x="360"/>
-        <item sd="0" x="361"/>
-        <item sd="0" x="362"/>
-        <item sd="0" x="363"/>
-        <item sd="0" x="364"/>
-        <item sd="0" x="365"/>
-        <item sd="0" x="366"/>
-        <item sd="0" x="367"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="15">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="3">
-    <field x="7"/>
-    <field x="6"/>
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="13">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Request Date" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="5" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="10" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Requestor" xr10:uid="{0C35168A-CAC8-43AE-AA23-C90071890A78}" sourceName="Requestor">
   <pivotTables>
@@ -20741,7 +20762,7 @@
     <tabColor theme="9" tint="0.39997558519241921"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R96"/>
+  <dimension ref="A1:R98"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -20814,10 +20835,10 @@
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" s="124" t="s">
+      <c r="A2" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="115" t="s">
+      <c r="B2" s="108" t="s">
         <v>18</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -20849,8 +20870,8 @@
       <c r="Q2" s="24"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" s="125"/>
-      <c r="B3" s="116"/>
+      <c r="A3" s="121"/>
+      <c r="B3" s="109"/>
       <c r="C3" s="4" t="s">
         <v>22</v>
       </c>
@@ -20880,8 +20901,8 @@
       <c r="Q3" s="4"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" s="126"/>
-      <c r="B4" s="117"/>
+      <c r="A4" s="122"/>
+      <c r="B4" s="110"/>
       <c r="C4" s="4" t="s">
         <v>23</v>
       </c>
@@ -21025,10 +21046,10 @@
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A8" s="115" t="s">
+      <c r="A8" s="108" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="115" t="s">
+      <c r="B8" s="108" t="s">
         <v>37</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -21060,8 +21081,8 @@
       <c r="Q8" s="4"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" s="116"/>
-      <c r="B9" s="116"/>
+      <c r="A9" s="109"/>
+      <c r="B9" s="109"/>
       <c r="C9" s="4" t="s">
         <v>39</v>
       </c>
@@ -21091,8 +21112,8 @@
       <c r="Q9" s="4"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A10" s="116"/>
-      <c r="B10" s="116"/>
+      <c r="A10" s="109"/>
+      <c r="B10" s="109"/>
       <c r="C10" s="4" t="s">
         <v>41</v>
       </c>
@@ -21122,10 +21143,10 @@
       <c r="Q10" s="4"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A11" s="121" t="s">
+      <c r="A11" s="114" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="121" t="s">
+      <c r="B11" s="114" t="s">
         <v>45</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -21157,8 +21178,8 @@
       <c r="Q11" s="4"/>
     </row>
     <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="117"/>
-      <c r="B12" s="117"/>
+      <c r="A12" s="110"/>
+      <c r="B12" s="110"/>
       <c r="C12" s="4" t="s">
         <v>46</v>
       </c>
@@ -21188,10 +21209,10 @@
       <c r="Q12" s="4"/>
     </row>
     <row r="13" spans="1:18" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="115" t="s">
+      <c r="A13" s="108" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="115" t="s">
+      <c r="B13" s="108" t="s">
         <v>50</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -21227,8 +21248,8 @@
       </c>
     </row>
     <row r="14" spans="1:18" ht="76.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="116"/>
-      <c r="B14" s="116"/>
+      <c r="A14" s="109"/>
+      <c r="B14" s="109"/>
       <c r="C14" s="4" t="s">
         <v>54</v>
       </c>
@@ -21262,8 +21283,8 @@
       </c>
     </row>
     <row r="15" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="116"/>
-      <c r="B15" s="116"/>
+      <c r="A15" s="109"/>
+      <c r="B15" s="109"/>
       <c r="C15" s="4" t="s">
         <v>56</v>
       </c>
@@ -21293,8 +21314,8 @@
       <c r="Q15" s="4"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A16" s="117"/>
-      <c r="B16" s="117"/>
+      <c r="A16" s="110"/>
+      <c r="B16" s="110"/>
       <c r="C16" s="4" t="s">
         <v>57</v>
       </c>
@@ -21324,10 +21345,10 @@
       <c r="Q16" s="4"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A17" s="115" t="s">
+      <c r="A17" s="108" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="115" t="s">
+      <c r="B17" s="108" t="s">
         <v>59</v>
       </c>
       <c r="C17" s="5" t="s">
@@ -21361,8 +21382,8 @@
       <c r="Q17" s="4"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A18" s="117"/>
-      <c r="B18" s="117"/>
+      <c r="A18" s="110"/>
+      <c r="B18" s="110"/>
       <c r="C18" s="5" t="s">
         <v>61</v>
       </c>
@@ -21394,13 +21415,13 @@
       <c r="Q18" s="4"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A19" s="121" t="s">
+      <c r="A19" s="114" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="121" t="s">
+      <c r="B19" s="114" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="127" t="s">
+      <c r="C19" s="123" t="s">
         <v>23</v>
       </c>
       <c r="D19" s="5" t="s">
@@ -21429,9 +21450,9 @@
       <c r="Q19" s="4"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A20" s="121"/>
-      <c r="B20" s="121"/>
-      <c r="C20" s="127"/>
+      <c r="A20" s="114"/>
+      <c r="B20" s="114"/>
+      <c r="C20" s="123"/>
       <c r="D20" s="5" t="s">
         <v>65</v>
       </c>
@@ -21458,9 +21479,9 @@
       <c r="Q20" s="4"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A21" s="121"/>
-      <c r="B21" s="121"/>
-      <c r="C21" s="127"/>
+      <c r="A21" s="114"/>
+      <c r="B21" s="114"/>
+      <c r="C21" s="123"/>
       <c r="D21" s="5" t="s">
         <v>66</v>
       </c>
@@ -21487,10 +21508,10 @@
       <c r="Q21" s="4"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A22" s="121" t="s">
+      <c r="A22" s="114" t="s">
         <v>67</v>
       </c>
-      <c r="B22" s="121" t="s">
+      <c r="B22" s="114" t="s">
         <v>68</v>
       </c>
       <c r="C22" s="4" t="s">
@@ -21524,8 +21545,8 @@
       <c r="Q22" s="4"/>
     </row>
     <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="121"/>
-      <c r="B23" s="121"/>
+      <c r="A23" s="114"/>
+      <c r="B23" s="114"/>
       <c r="C23" s="4" t="s">
         <v>41</v>
       </c>
@@ -21558,10 +21579,10 @@
       <c r="R23" s="9"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A24" s="121" t="s">
+      <c r="A24" s="114" t="s">
         <v>73</v>
       </c>
-      <c r="B24" s="121" t="s">
+      <c r="B24" s="114" t="s">
         <v>74</v>
       </c>
       <c r="C24" s="4" t="s">
@@ -21596,8 +21617,8 @@
       <c r="R24" s="9"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A25" s="117"/>
-      <c r="B25" s="117"/>
+      <c r="A25" s="110"/>
+      <c r="B25" s="110"/>
       <c r="C25" s="4" t="s">
         <v>41</v>
       </c>
@@ -21628,7 +21649,7 @@
       <c r="R25" s="9"/>
     </row>
     <row r="26" spans="1:18" ht="38.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="115" t="s">
+      <c r="A26" s="108" t="s">
         <v>77</v>
       </c>
       <c r="B26" s="21" t="s">
@@ -21667,7 +21688,7 @@
       </c>
     </row>
     <row r="27" spans="1:18" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="117"/>
+      <c r="A27" s="110"/>
       <c r="B27" s="21" t="s">
         <v>78</v>
       </c>
@@ -21754,10 +21775,10 @@
       <c r="Q28" s="12"/>
     </row>
     <row r="29" spans="1:18" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="121" t="s">
+      <c r="A29" s="114" t="s">
         <v>85</v>
       </c>
-      <c r="B29" s="121" t="s">
+      <c r="B29" s="114" t="s">
         <v>86</v>
       </c>
       <c r="C29" s="4" t="s">
@@ -21791,8 +21812,8 @@
       <c r="Q29" s="4"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A30" s="116"/>
-      <c r="B30" s="116"/>
+      <c r="A30" s="109"/>
+      <c r="B30" s="109"/>
       <c r="C30" s="4" t="s">
         <v>88</v>
       </c>
@@ -21824,8 +21845,8 @@
       <c r="Q30" s="4"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A31" s="116"/>
-      <c r="B31" s="116"/>
+      <c r="A31" s="109"/>
+      <c r="B31" s="109"/>
       <c r="C31" s="4" t="s">
         <v>88</v>
       </c>
@@ -21857,8 +21878,8 @@
       <c r="Q31" s="4"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A32" s="117"/>
-      <c r="B32" s="117"/>
+      <c r="A32" s="110"/>
+      <c r="B32" s="110"/>
       <c r="C32" s="4" t="s">
         <v>88</v>
       </c>
@@ -21999,10 +22020,10 @@
       <c r="Q35" s="13"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A36" s="115" t="s">
+      <c r="A36" s="108" t="s">
         <v>101</v>
       </c>
-      <c r="B36" s="115" t="s">
+      <c r="B36" s="108" t="s">
         <v>102</v>
       </c>
       <c r="C36" s="4" t="s">
@@ -22034,8 +22055,8 @@
       <c r="Q36" s="4"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A37" s="117"/>
-      <c r="B37" s="117"/>
+      <c r="A37" s="110"/>
+      <c r="B37" s="110"/>
       <c r="C37" s="4" t="s">
         <v>104</v>
       </c>
@@ -22104,10 +22125,10 @@
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A39" s="115" t="s">
+      <c r="A39" s="108" t="s">
         <v>109</v>
       </c>
-      <c r="B39" s="115" t="s">
+      <c r="B39" s="108" t="s">
         <v>110</v>
       </c>
       <c r="C39" s="4" t="s">
@@ -22141,8 +22162,8 @@
       <c r="Q39" s="4"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A40" s="116"/>
-      <c r="B40" s="116"/>
+      <c r="A40" s="109"/>
+      <c r="B40" s="109"/>
       <c r="C40" s="4" t="s">
         <v>22</v>
       </c>
@@ -22174,8 +22195,8 @@
       <c r="Q40" s="4"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A41" s="117"/>
-      <c r="B41" s="117"/>
+      <c r="A41" s="110"/>
+      <c r="B41" s="110"/>
       <c r="C41" s="4" t="s">
         <v>22</v>
       </c>
@@ -22359,10 +22380,10 @@
       <c r="Q45" s="13"/>
     </row>
     <row r="46" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="115" t="s">
+      <c r="A46" s="108" t="s">
         <v>124</v>
       </c>
-      <c r="B46" s="115" t="s">
+      <c r="B46" s="108" t="s">
         <v>125</v>
       </c>
       <c r="C46" s="4" t="s">
@@ -22396,8 +22417,8 @@
       </c>
     </row>
     <row r="47" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="117"/>
-      <c r="B47" s="117"/>
+      <c r="A47" s="110"/>
+      <c r="B47" s="110"/>
       <c r="C47" s="4" t="s">
         <v>38</v>
       </c>
@@ -22429,10 +22450,10 @@
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A48" s="128" t="s">
+      <c r="A48" s="124" t="s">
         <v>126</v>
       </c>
-      <c r="B48" s="128" t="s">
+      <c r="B48" s="124" t="s">
         <v>127</v>
       </c>
       <c r="C48" s="4" t="s">
@@ -22464,8 +22485,8 @@
       <c r="Q48" s="4"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A49" s="129"/>
-      <c r="B49" s="129"/>
+      <c r="A49" s="125"/>
+      <c r="B49" s="125"/>
       <c r="C49" s="4" t="s">
         <v>96</v>
       </c>
@@ -22622,10 +22643,10 @@
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A53" s="115" t="s">
+      <c r="A53" s="108" t="s">
         <v>141</v>
       </c>
-      <c r="B53" s="115" t="s">
+      <c r="B53" s="108" t="s">
         <v>142</v>
       </c>
       <c r="C53" s="12" t="s">
@@ -22659,8 +22680,8 @@
       <c r="Q53" s="20"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A54" s="116"/>
-      <c r="B54" s="116"/>
+      <c r="A54" s="109"/>
+      <c r="B54" s="109"/>
       <c r="C54" s="12" t="s">
         <v>119</v>
       </c>
@@ -22692,8 +22713,8 @@
       <c r="Q54" s="20"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A55" s="117"/>
-      <c r="B55" s="117"/>
+      <c r="A55" s="110"/>
+      <c r="B55" s="110"/>
       <c r="C55" s="12" t="s">
         <v>146</v>
       </c>
@@ -22797,7 +22818,7 @@
       <c r="Q57" s="20"/>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A58" s="115" t="s">
+      <c r="A58" s="108" t="s">
         <v>153</v>
       </c>
       <c r="B58" s="38" t="s">
@@ -22834,7 +22855,7 @@
       <c r="Q58" s="21"/>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A59" s="116"/>
+      <c r="A59" s="109"/>
       <c r="B59" s="39"/>
       <c r="C59" s="4" t="s">
         <v>33</v>
@@ -22867,7 +22888,7 @@
       <c r="Q59" s="21"/>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A60" s="116"/>
+      <c r="A60" s="109"/>
       <c r="B60" s="39"/>
       <c r="C60" s="4" t="s">
         <v>157</v>
@@ -22900,7 +22921,7 @@
       <c r="Q60" s="21"/>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A61" s="116"/>
+      <c r="A61" s="109"/>
       <c r="B61" s="39"/>
       <c r="C61" s="4" t="s">
         <v>159</v>
@@ -22933,7 +22954,7 @@
       <c r="Q61" s="21"/>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A62" s="117"/>
+      <c r="A62" s="110"/>
       <c r="B62" s="101"/>
       <c r="C62" s="4" t="s">
         <v>161</v>
@@ -22966,10 +22987,10 @@
       <c r="Q62" s="21"/>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A63" s="122" t="s">
+      <c r="A63" s="115" t="s">
         <v>162</v>
       </c>
-      <c r="B63" s="122" t="s">
+      <c r="B63" s="115" t="s">
         <v>163</v>
       </c>
       <c r="C63" s="41" t="s">
@@ -23001,8 +23022,8 @@
       <c r="Q63" s="6"/>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A64" s="123"/>
-      <c r="B64" s="123"/>
+      <c r="A64" s="116"/>
+      <c r="B64" s="116"/>
       <c r="C64" s="41" t="s">
         <v>166</v>
       </c>
@@ -23069,10 +23090,10 @@
       </c>
     </row>
     <row r="66" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="118" t="s">
+      <c r="A66" s="111" t="s">
         <v>171</v>
       </c>
-      <c r="B66" s="118" t="s">
+      <c r="B66" s="111" t="s">
         <v>172</v>
       </c>
       <c r="C66" s="4" t="s">
@@ -23108,8 +23129,8 @@
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A67" s="119"/>
-      <c r="B67" s="119"/>
+      <c r="A67" s="112"/>
+      <c r="B67" s="112"/>
       <c r="C67" s="4" t="s">
         <v>33</v>
       </c>
@@ -23141,8 +23162,8 @@
       <c r="Q67" s="6"/>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A68" s="120"/>
-      <c r="B68" s="120"/>
+      <c r="A68" s="113"/>
+      <c r="B68" s="113"/>
       <c r="C68" s="4" t="s">
         <v>19</v>
       </c>
@@ -23285,10 +23306,10 @@
       <c r="Q71" s="4"/>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A72" s="118" t="s">
+      <c r="A72" s="111" t="s">
         <v>186</v>
       </c>
-      <c r="B72" s="118" t="s">
+      <c r="B72" s="111" t="s">
         <v>187</v>
       </c>
       <c r="C72" s="4" t="s">
@@ -23320,8 +23341,8 @@
       <c r="Q72" s="4"/>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A73" s="119"/>
-      <c r="B73" s="119"/>
+      <c r="A73" s="112"/>
+      <c r="B73" s="112"/>
       <c r="C73" s="4" t="s">
         <v>139</v>
       </c>
@@ -23351,8 +23372,8 @@
       <c r="Q73" s="4"/>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A74" s="120"/>
-      <c r="B74" s="120"/>
+      <c r="A74" s="113"/>
+      <c r="B74" s="113"/>
       <c r="C74" s="4" t="s">
         <v>188</v>
       </c>
@@ -23383,7 +23404,9 @@
       <c r="A75" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="B75" s="4"/>
+      <c r="B75" s="4" t="s">
+        <v>189</v>
+      </c>
       <c r="C75" s="4" t="s">
         <v>41</v>
       </c>
@@ -23448,10 +23471,10 @@
       <c r="Q76" s="4"/>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A77" s="118" t="s">
+      <c r="A77" s="111" t="s">
         <v>194</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="117" t="s">
         <v>195</v>
       </c>
       <c r="C77" s="4" t="s">
@@ -23483,8 +23506,8 @@
       <c r="Q77" s="6"/>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A78" s="119"/>
-      <c r="B78" s="4"/>
+      <c r="A78" s="112"/>
+      <c r="B78" s="118"/>
       <c r="C78" s="4" t="s">
         <v>197</v>
       </c>
@@ -23516,8 +23539,8 @@
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A79" s="120"/>
-      <c r="B79" s="4"/>
+      <c r="A79" s="113"/>
+      <c r="B79" s="119"/>
       <c r="C79" s="4" t="s">
         <v>199</v>
       </c>
@@ -23547,7 +23570,7 @@
       <c r="Q79" s="6"/>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A80" s="118" t="s">
+      <c r="A80" s="111" t="s">
         <v>201</v>
       </c>
       <c r="B80" s="4" t="s">
@@ -23582,7 +23605,7 @@
       <c r="Q80" s="6"/>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A81" s="120"/>
+      <c r="A81" s="113"/>
       <c r="B81" s="4" t="s">
         <v>204</v>
       </c>
@@ -23615,10 +23638,10 @@
       <c r="Q81" s="6"/>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A82" s="118" t="s">
+      <c r="A82" s="111" t="s">
         <v>207</v>
       </c>
-      <c r="B82" s="118" t="s">
+      <c r="B82" s="111" t="s">
         <v>208</v>
       </c>
       <c r="C82" s="4" t="s">
@@ -23654,8 +23677,8 @@
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A83" s="119"/>
-      <c r="B83" s="119"/>
+      <c r="A83" s="112"/>
+      <c r="B83" s="112"/>
       <c r="C83" s="4" t="s">
         <v>211</v>
       </c>
@@ -23687,8 +23710,8 @@
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A84" s="119"/>
-      <c r="B84" s="119"/>
+      <c r="A84" s="112"/>
+      <c r="B84" s="112"/>
       <c r="C84" s="4" t="s">
         <v>214</v>
       </c>
@@ -23722,8 +23745,8 @@
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A85" s="120"/>
-      <c r="B85" s="120"/>
+      <c r="A85" s="113"/>
+      <c r="B85" s="113"/>
       <c r="C85" s="4" t="s">
         <v>215</v>
       </c>
@@ -23757,10 +23780,10 @@
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A86" s="4" t="s">
+      <c r="A86" s="117" t="s">
         <v>216</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="117" t="s">
         <v>217</v>
       </c>
       <c r="C86" s="4" t="s">
@@ -23796,8 +23819,8 @@
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A87" s="4"/>
-      <c r="B87" s="4"/>
+      <c r="A87" s="119"/>
+      <c r="B87" s="119"/>
       <c r="C87" s="4" t="s">
         <v>220</v>
       </c>
@@ -23834,7 +23857,9 @@
       <c r="A88" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="B88" s="4"/>
+      <c r="B88" s="4" t="s">
+        <v>222</v>
+      </c>
       <c r="C88" s="4" t="s">
         <v>223</v>
       </c>
@@ -23901,10 +23926,12 @@
       <c r="Q89" s="6"/>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A90" s="4" t="s">
+      <c r="A90" s="117" t="s">
         <v>533</v>
       </c>
-      <c r="B90" s="4"/>
+      <c r="B90" s="117" t="s">
+        <v>533</v>
+      </c>
       <c r="C90" s="4" t="s">
         <v>538</v>
       </c>
@@ -23936,8 +23963,8 @@
       <c r="Q90" s="4"/>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A91" s="4"/>
-      <c r="B91" s="4"/>
+      <c r="A91" s="118"/>
+      <c r="B91" s="118"/>
       <c r="C91" s="4" t="s">
         <v>539</v>
       </c>
@@ -23969,8 +23996,8 @@
       <c r="Q91" s="4"/>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A92" s="4"/>
-      <c r="B92" s="4"/>
+      <c r="A92" s="119"/>
+      <c r="B92" s="119"/>
       <c r="C92" s="4" t="s">
         <v>540</v>
       </c>
@@ -24039,10 +24066,12 @@
       <c r="Q93" s="4"/>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A94" s="4" t="s">
+      <c r="A94" s="117" t="s">
         <v>543</v>
       </c>
-      <c r="B94" s="4"/>
+      <c r="B94" s="117" t="s">
+        <v>543</v>
+      </c>
       <c r="C94" s="4" t="s">
         <v>19</v>
       </c>
@@ -24064,8 +24093,8 @@
       <c r="Q94" s="4"/>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A95" s="4"/>
-      <c r="B95" s="4"/>
+      <c r="A95" s="118"/>
+      <c r="B95" s="118"/>
       <c r="C95" s="4" t="s">
         <v>146</v>
       </c>
@@ -24087,8 +24116,8 @@
       <c r="Q95" s="4"/>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A96" s="4"/>
-      <c r="B96" s="4"/>
+      <c r="A96" s="119"/>
+      <c r="B96" s="119"/>
       <c r="C96" s="4" t="s">
         <v>41</v>
       </c>
@@ -24109,9 +24138,64 @@
       <c r="P96" s="4"/>
       <c r="Q96" s="4"/>
     </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A97" s="126" t="s">
+        <v>546</v>
+      </c>
+      <c r="B97" s="6"/>
+      <c r="C97" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D97" s="107">
+        <v>1001276729875010</v>
+      </c>
+      <c r="E97" s="6"/>
+      <c r="F97" s="6"/>
+      <c r="G97" s="6"/>
+      <c r="H97" s="6"/>
+      <c r="I97" s="6"/>
+      <c r="J97" s="6"/>
+      <c r="K97" s="6"/>
+      <c r="L97" s="6"/>
+      <c r="M97" s="6"/>
+      <c r="N97" s="6"/>
+      <c r="O97" s="6"/>
+      <c r="P97" s="6"/>
+      <c r="Q97" s="6"/>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A98" s="127"/>
+      <c r="B98" s="6"/>
+      <c r="C98" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D98" s="107">
+        <v>592215339380</v>
+      </c>
+      <c r="E98" s="6"/>
+      <c r="F98" s="6"/>
+      <c r="G98" s="6"/>
+      <c r="H98" s="6"/>
+      <c r="I98" s="6"/>
+      <c r="J98" s="6"/>
+      <c r="K98" s="6"/>
+      <c r="L98" s="6"/>
+      <c r="M98" s="6"/>
+      <c r="N98" s="6"/>
+      <c r="O98" s="6"/>
+      <c r="P98" s="6"/>
+      <c r="Q98" s="6"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:Q96" xr:uid="{17FB2E45-7FCC-4B4B-AD71-D79ACD2C0ED5}"/>
-  <mergeCells count="41">
+  <mergeCells count="49">
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="A86:A87"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="A90:A92"/>
+    <mergeCell ref="B90:B92"/>
+    <mergeCell ref="A94:A96"/>
+    <mergeCell ref="B94:B96"/>
     <mergeCell ref="C19:C21"/>
     <mergeCell ref="B22:B23"/>
     <mergeCell ref="B24:B25"/>
@@ -24146,6 +24230,7 @@
     <mergeCell ref="A66:A68"/>
     <mergeCell ref="A72:A74"/>
     <mergeCell ref="B72:B74"/>
+    <mergeCell ref="B77:B79"/>
     <mergeCell ref="A13:A16"/>
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="A58:A62"/>
@@ -24172,7 +24257,7 @@
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A2:AG55"/>
+  <dimension ref="A2:AG56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -24195,26 +24280,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A2" s="108" t="s">
+      <c r="A2" s="129" t="s">
         <v>224</v>
       </c>
-      <c r="B2" s="108"/>
-      <c r="C2" s="108"/>
-      <c r="D2" s="108"/>
-      <c r="E2" s="108"/>
-      <c r="F2" s="108"/>
-      <c r="G2" s="108"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="108"/>
-      <c r="J2" s="108"/>
-      <c r="K2" s="108"/>
-      <c r="L2" s="108"/>
-      <c r="M2" s="108"/>
-      <c r="N2" s="108"/>
-      <c r="O2" s="108"/>
-      <c r="P2" s="108"/>
-      <c r="Q2" s="108"/>
-      <c r="R2" s="108"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="129"/>
+      <c r="P2" s="129"/>
+      <c r="Q2" s="129"/>
+      <c r="R2" s="129"/>
       <c r="S2" s="29"/>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
@@ -24224,26 +24309,26 @@
       <c r="B3" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="C3" s="109" t="s">
+      <c r="C3" s="130" t="s">
         <v>227</v>
       </c>
-      <c r="D3" s="110"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="110"/>
-      <c r="H3" s="110"/>
-      <c r="I3" s="110"/>
-      <c r="J3" s="110"/>
-      <c r="K3" s="110"/>
-      <c r="L3" s="110"/>
-      <c r="M3" s="110"/>
-      <c r="N3" s="110"/>
-      <c r="O3" s="111" t="s">
+      <c r="D3" s="131"/>
+      <c r="E3" s="131"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="131"/>
+      <c r="H3" s="131"/>
+      <c r="I3" s="131"/>
+      <c r="J3" s="131"/>
+      <c r="K3" s="131"/>
+      <c r="L3" s="131"/>
+      <c r="M3" s="131"/>
+      <c r="N3" s="131"/>
+      <c r="O3" s="132" t="s">
         <v>228</v>
       </c>
-      <c r="P3" s="112"/>
-      <c r="Q3" s="112"/>
-      <c r="R3" s="113"/>
+      <c r="P3" s="133"/>
+      <c r="Q3" s="133"/>
+      <c r="R3" s="134"/>
       <c r="S3" s="29"/>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
@@ -24459,10 +24544,10 @@
         <v>235</v>
       </c>
       <c r="S7" s="28"/>
-      <c r="Y7" s="107" t="s">
+      <c r="Y7" s="128" t="s">
         <v>237</v>
       </c>
-      <c r="Z7" s="107"/>
+      <c r="Z7" s="128"/>
       <c r="AD7" t="s">
         <v>238</v>
       </c>
@@ -24762,10 +24847,10 @@
         <v>235</v>
       </c>
       <c r="S12" s="28"/>
-      <c r="Y12" s="107" t="s">
+      <c r="Y12" s="128" t="s">
         <v>247</v>
       </c>
-      <c r="Z12" s="107"/>
+      <c r="Z12" s="128"/>
       <c r="AD12" t="s">
         <v>8</v>
       </c>
@@ -25037,10 +25122,10 @@
         <v>235</v>
       </c>
       <c r="S17" s="28"/>
-      <c r="Y17" s="107" t="s">
+      <c r="Y17" s="128" t="s">
         <v>251</v>
       </c>
-      <c r="Z17" s="107"/>
+      <c r="Z17" s="128"/>
       <c r="AD17" t="s">
         <v>13</v>
       </c>
@@ -25245,8 +25330,8 @@
         <v>235</v>
       </c>
       <c r="S21" s="28"/>
-      <c r="Y21" s="114"/>
-      <c r="Z21" s="114"/>
+      <c r="Y21" s="135"/>
+      <c r="Z21" s="135"/>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
@@ -25291,10 +25376,10 @@
         <v>235</v>
       </c>
       <c r="S22" s="28"/>
-      <c r="Y22" s="107" t="s">
+      <c r="Y22" s="128" t="s">
         <v>252</v>
       </c>
-      <c r="Z22" s="107"/>
+      <c r="Z22" s="128"/>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="16">
@@ -25534,10 +25619,10 @@
         <v>254</v>
       </c>
       <c r="S27" s="28"/>
-      <c r="Y27" s="107" t="s">
+      <c r="Y27" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="Z27" s="107"/>
+      <c r="Z27" s="128"/>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="16">
@@ -25795,10 +25880,10 @@
         <v>235</v>
       </c>
       <c r="S32" s="28"/>
-      <c r="Y32" s="107" t="s">
+      <c r="Y32" s="128" t="s">
         <v>255</v>
       </c>
-      <c r="Z32" s="107"/>
+      <c r="Z32" s="128"/>
       <c r="AC32" s="80"/>
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.25">
@@ -26059,10 +26144,10 @@
         <v>235</v>
       </c>
       <c r="S37" s="28"/>
-      <c r="Y37" s="107" t="s">
+      <c r="Y37" s="128" t="s">
         <v>256</v>
       </c>
-      <c r="Z37" s="107"/>
+      <c r="Z37" s="128"/>
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A38" s="16">
@@ -26297,10 +26382,10 @@
       <c r="R42" s="27" t="s">
         <v>235</v>
       </c>
-      <c r="Y42" s="107" t="s">
+      <c r="Y42" s="128" t="s">
         <v>258</v>
       </c>
-      <c r="Z42" s="107"/>
+      <c r="Z42" s="128"/>
     </row>
     <row r="43" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A43" s="16">
@@ -26549,10 +26634,10 @@
       <c r="R47" s="27" t="s">
         <v>235</v>
       </c>
-      <c r="Y47" s="107" t="s">
+      <c r="Y47" s="128" t="s">
         <v>262</v>
       </c>
-      <c r="Z47" s="107"/>
+      <c r="Z47" s="128"/>
     </row>
     <row r="48" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A48" s="16">
@@ -26934,6 +27019,51 @@
       <c r="Z55" s="23" t="e">
         <f>(Z53/Z54)*100</f>
         <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="56" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A56" s="16">
+        <v>51</v>
+      </c>
+      <c r="B56" s="17" t="s">
+        <v>546</v>
+      </c>
+      <c r="C56" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="D56" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="E56" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="F56" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="G56" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="H56" s="17"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="17"/>
+      <c r="K56" s="17"/>
+      <c r="L56" s="17"/>
+      <c r="M56" s="17"/>
+      <c r="N56" s="17"/>
+      <c r="O56" s="16" t="str">
+        <f t="shared" ref="O56" si="6">IF(COUNTIF(C56:N56, 0) = 1, "Yes", "No")</f>
+        <v>No</v>
+      </c>
+      <c r="P56" s="27" t="str">
+        <f t="shared" ref="P56" si="7">IF(COUNTIF(C56:N56, 0) = 2, "Yes", "No")</f>
+        <v>No</v>
+      </c>
+      <c r="Q56" s="27" t="str">
+        <f t="shared" ref="Q56" si="8">IF(COUNTIF(C56:N56, 0) &gt;= 3, "Yes", "No")</f>
+        <v>No</v>
+      </c>
+      <c r="R56" s="27" t="s">
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -26967,7 +27097,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="5" id="{652ED857-024D-4A9E-91E7-4B7D263A3981}">
+          <x14:cfRule type="iconSet" priority="6" id="{652ED857-024D-4A9E-91E7-4B7D263A3981}">
             <x14:iconSet showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -26986,7 +27116,7 @@
           <xm:sqref>C52:D52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="2" id="{AB669DED-D780-4B1B-B43B-57809700B86D}">
+          <x14:cfRule type="iconSet" priority="3" id="{AB669DED-D780-4B1B-B43B-57809700B86D}">
             <x14:iconSet showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -27005,7 +27135,26 @@
           <xm:sqref>C54:D55</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="11" id="{3D348A3B-BDD4-4B84-B3BD-199508CC71B5}">
+          <x14:cfRule type="iconSet" priority="1" id="{B1DECD3F-1399-47B7-BEE2-D01A5DBEE223}">
+            <x14:iconSet showValue="0" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num" gte="0">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3TrafficLights1" iconId="0"/>
+              <x14:cfIcon iconSet="5Quarters" iconId="0"/>
+              <x14:cfIcon iconSet="3TrafficLights1" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>C56:G56</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="12" id="{3D348A3B-BDD4-4B84-B3BD-199508CC71B5}">
             <x14:iconSet showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -27024,7 +27173,7 @@
           <xm:sqref>C48:H48 C47:N47</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="35" id="{CDC3E997-1982-4CEE-9FE3-F6BF82DD0CA7}">
+          <x14:cfRule type="iconSet" priority="36" id="{CDC3E997-1982-4CEE-9FE3-F6BF82DD0CA7}">
             <x14:iconSet showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -27043,7 +27192,7 @@
           <xm:sqref>C49:N51</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="3" id="{CE013053-2999-4138-8B48-9FF1DCBDE2D1}">
+          <x14:cfRule type="iconSet" priority="4" id="{CE013053-2999-4138-8B48-9FF1DCBDE2D1}">
             <x14:iconSet showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -27059,10 +27208,10 @@
               <x14:cfIcon iconSet="3TrafficLights1" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>C53:N53 G53:R55</xm:sqref>
+          <xm:sqref>C53:N53 G53:R55 O56:R56</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="25" id="{C9CFA181-79D3-41C5-96A0-9B583BEB4AC3}">
+          <x14:cfRule type="iconSet" priority="26" id="{C9CFA181-79D3-41C5-96A0-9B583BEB4AC3}">
             <x14:iconSet showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -27081,7 +27230,7 @@
           <xm:sqref>E42:E46 F34:F46 G42:G46 P40:R46 C32:D46 E32:G34 I48:N48 N48:N51 C15:G31 C5:N14 H36:N46 E36:G42 E35:N35 H15:N34</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="12" id="{BCF9F5FB-2055-44F5-9963-EA1BDECC4D13}">
+          <x14:cfRule type="iconSet" priority="13" id="{BCF9F5FB-2055-44F5-9963-EA1BDECC4D13}">
             <x14:iconSet showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -27100,7 +27249,7 @@
           <xm:sqref>E43</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="1" id="{213BC6D1-5917-49C9-94C4-14838649036B}">
+          <x14:cfRule type="iconSet" priority="2" id="{213BC6D1-5917-49C9-94C4-14838649036B}">
             <x14:iconSet showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -27119,7 +27268,7 @@
           <xm:sqref>E54:F55</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="4" id="{BABBA284-CE3C-493A-B407-9B46A1B8C4E5}">
+          <x14:cfRule type="iconSet" priority="5" id="{BABBA284-CE3C-493A-B407-9B46A1B8C4E5}">
             <x14:iconSet showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -27138,7 +27287,7 @@
           <xm:sqref>E52:N52</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="19" id="{ED424E51-9A03-4C4C-B2CC-0524865B80D4}">
+          <x14:cfRule type="iconSet" priority="20" id="{ED424E51-9A03-4C4C-B2CC-0524865B80D4}">
             <x14:iconSet showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -27157,7 +27306,7 @@
           <xm:sqref>U4</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="18" id="{8BCBC3F4-1A34-4D95-A412-357D371F4FEB}">
+          <x14:cfRule type="iconSet" priority="19" id="{8BCBC3F4-1A34-4D95-A412-357D371F4FEB}">
             <x14:iconSet showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -27176,7 +27325,7 @@
           <xm:sqref>U5</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="iconSet" priority="17" id="{82422374-795F-4BB6-BB12-AB5CA00130A7}">
+          <x14:cfRule type="iconSet" priority="18" id="{82422374-795F-4BB6-BB12-AB5CA00130A7}">
             <x14:iconSet showValue="0" custom="1">
               <x14:cfvo type="percent">
                 <xm:f>0</xm:f>
@@ -34128,7 +34277,7 @@
       <c r="H19" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I19" s="127" t="s">
+      <c r="I19" s="123" t="s">
         <v>23</v>
       </c>
       <c r="J19" s="5" t="s">
@@ -34150,7 +34299,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="21"/>
-      <c r="I20" s="127"/>
+      <c r="I20" s="123"/>
       <c r="J20" s="5" t="s">
         <v>65</v>
       </c>
@@ -34170,7 +34319,7 @@
         <v>1</v>
       </c>
       <c r="H21" s="21"/>
-      <c r="I21" s="127"/>
+      <c r="I21" s="123"/>
       <c r="J21" s="5" t="s">
         <v>66</v>
       </c>
